--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="96">
   <si>
     <t xml:space="preserve">Botcake content series</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t xml:space="preserve">Targets one industry in the US and Canada; supports med spa prospecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dijaedadula.com/ai-automation-clinics-med-spas</t>
   </si>
   <si>
     <t xml:space="preserve">How to Package and Price AI Automation Services (Freelancer and Agency Guide)</t>
@@ -320,7 +323,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +378,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -456,7 +466,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,6 +511,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,7 +524,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -553,6 +567,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC8E6C9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1495,11 +1517,15 @@
         <v>18</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="7"/>
+      <c r="K11" s="7" t="n">
+        <v>46310</v>
+      </c>
       <c r="L11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1510,16 +1536,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>18</v>
@@ -1528,7 +1554,7 @@
         <v>53</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="7" t="n">
@@ -1544,19 +1570,19 @@
         <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>19</v>
@@ -1574,16 +1600,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>80</v>
@@ -1602,7 +1628,7 @@
       </c>
       <c r="B16" s="9" t="str">
         <f aca="false">COUNTIF(H5:H14,"Published")&amp;" of "&amp;COUNTA(C5:C14)</f>
-        <v>3 of 10</v>
+        <v>4 of 10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1630,7 +1656,8 @@
   <hyperlinks>
     <hyperlink ref="I5" r:id="rId1" display="https://www.dijaedadula.com/ai-agent-instructions-template"/>
     <hyperlink ref="I6" r:id="rId2" display="https://www.dijaedadula.com/chatbot-roi-metrics"/>
-    <hyperlink ref="I12" r:id="rId3" display="https://www.dijaedadula.com/price-ai-automation-services"/>
+    <hyperlink ref="I11" r:id="rId3" display="https://www.dijaedadula.com/ai-automation-clinics-med-spas"/>
+    <hyperlink ref="I12" r:id="rId4" display="https://www.dijaedadula.com/price-ai-automation-services"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1639,6 +1666,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -709,12 +709,18 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/ai-chatbot-cost</t>
+        </is>
+      </c>
       <c r="J6" s="18" t="n"/>
-      <c r="K6" s="20" t="n"/>
+      <c r="K6" s="19" t="n">
+        <v>46315</v>
+      </c>
       <c r="L6" s="18" t="n"/>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="13">
@@ -1090,6 +1096,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -757,12 +757,18 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/stop-bogus-cod-orders</t>
+        </is>
+      </c>
       <c r="J7" s="18" t="n"/>
-      <c r="K7" s="20" t="n"/>
+      <c r="K7" s="19" t="n">
+        <v>46316</v>
+      </c>
       <c r="L7" s="18" t="n"/>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="13">
@@ -1097,6 +1103,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -847,12 +847,18 @@
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/chatbot-sound-human</t>
+        </is>
+      </c>
       <c r="J9" s="18" t="n"/>
-      <c r="K9" s="20" t="n"/>
+      <c r="K9" s="19" t="n">
+        <v>46317</v>
+      </c>
       <c r="L9" s="18" t="n"/>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="13">
@@ -1104,6 +1110,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -895,12 +895,18 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/ai-chatbot-human-handoff</t>
+        </is>
+      </c>
       <c r="J10" s="18" t="n"/>
-      <c r="K10" s="20" t="n"/>
+      <c r="K10" s="19" t="n">
+        <v>46318</v>
+      </c>
       <c r="L10" s="18" t="n"/>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="13">
@@ -1111,6 +1117,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId5"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -1069,12 +1069,18 @@
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/blog-traffic-to-chat-leads</t>
+        </is>
+      </c>
       <c r="J14" s="18" t="n"/>
-      <c r="K14" s="20" t="n"/>
+      <c r="K14" s="19" t="n">
+        <v>46319</v>
+      </c>
       <c r="L14" s="18" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="13">
@@ -1118,6 +1124,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -1486,12 +1486,18 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/chatrace-vs-chatbotbuilder</t>
+        </is>
+      </c>
       <c r="J10" s="18" t="n"/>
-      <c r="K10" s="20" t="n"/>
+      <c r="K10" s="19" t="n">
+        <v>46320</v>
+      </c>
       <c r="L10" s="18" t="n"/>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="13">
@@ -1712,8 +1718,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" display="https://www.dijaedadula.com/ai-agent-instructions-template" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" display="https://www.dijaedadula.com/chatbot-roi-metrics" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" display="https://www.dijaedadula.com/ai-automation-clinics-med-spas" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" display="https://www.dijaedadula.com/price-ai-automation-services" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" display="https://www.dijaedadula.com/ai-automation-clinics-med-spas" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" display="https://www.dijaedadula.com/price-ai-automation-services" r:id="rId5"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -1672,33 +1672,88 @@
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/mcp-ai-agent-business-tools</t>
+        </is>
+      </c>
       <c r="J14" s="18" t="n"/>
-      <c r="K14" s="20" t="n"/>
+      <c r="K14" s="19" t="n">
+        <v>46322</v>
+      </c>
       <c r="L14" s="18" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="13">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>How to Ground an AI Agent in Your Business Knowledge (RAG Explained for Business Owners)</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Solution-aware</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>RAG for business, AI agent knowledge base</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Shows Dijae's long-standing knowledge-base (RAG) agent work; uses his own Botcake Knowledge screenshots; added by Dijae Oct 27 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="B16" s="22">
-        <f>COUNTIF(H5:H14,"Published")&amp;" of "&amp;COUNTA(C5:C14)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/rag-ai-agent-business-knowledge</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="19" t="n">
+        <v>46322</v>
+      </c>
+      <c r="L15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="13"/>
     <row r="17" ht="15" customHeight="1" s="13">
       <c r="A17" s="21" t="inlineStr">
         <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>COUNTIF(H5:H15,"Published")&amp;" of "&amp;COUNTA(C5:C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
           <t>Need recording</t>
         </is>
       </c>
-      <c r="B17" s="22">
-        <f>COUNTIF(G5:G14,"Yes*")</f>
+      <c r="B18" s="22">
+        <f>COUNTIF(G5:G15,"Yes*")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1765,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Planned,Recording needed,Drafting,Published"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1721,6 +1776,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" display="https://www.dijaedadula.com/ai-automation-clinics-med-spas" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" display="https://www.dijaedadula.com/price-ai-automation-services" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId7"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -1859,12 +1859,18 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/ai-agent-monitoring-weekly-review</t>
+        </is>
+      </c>
       <c r="J18" s="17" t="n"/>
-      <c r="K18" s="19" t="n"/>
+      <c r="K18" s="22" t="n">
+        <v>46325</v>
+      </c>
       <c r="L18" s="17" t="inlineStr">
         <is>
           <t>Added by Dijae Oct 28 2026</t>
@@ -2330,6 +2336,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" display="https://www.dijaedadula.com/rag-ai-agent-business-knowledge" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" display="https://www.dijaedadula.com/ai-agent-guardrails" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId10"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/checklist/Blog content checklist.xlsx
+++ b/checklist/Blog content checklist.xlsx
@@ -1911,12 +1911,18 @@
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dijaedadula.com/crm-pipeline-stages-service-business</t>
+        </is>
+      </c>
       <c r="J19" s="17" t="n"/>
-      <c r="K19" s="19" t="n"/>
+      <c r="K19" s="22" t="n">
+        <v>46326</v>
+      </c>
       <c r="L19" s="17" t="inlineStr">
         <is>
           <t>Added by Dijae Oct 28 2026</t>
@@ -2337,6 +2343,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" display="https://www.dijaedadula.com/ai-agent-guardrails" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId11"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
